--- a/docs/audit/AUDIT-watchtower-2026-10-06.xlsx
+++ b/docs/audit/AUDIT-watchtower-2026-10-06.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Publication UE" sheetId="3" r:id="rId3"/>
     <sheet name="Repos GitHub" sheetId="4" r:id="rId4"/>
     <sheet name="Ce qui existe - cout" sheetId="5" r:id="rId5"/>
+    <sheet name="CATALOGUE OUTILS" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -4786,4 +4787,7444 @@
   </sheetData>
   <autoFilter ref="A1:H22"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catégorie</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sous-catégorie</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outil ou source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coût</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte ou clé</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front-only</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chantier</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce qu'on en tire</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statut</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priorité</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confiance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CesiumJS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apache-2.0</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non (le moteur)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notre moteur actuel</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">openglobus</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apache-2.0</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alternative légère à Cesium, de la planète à l'abeille</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carte 2D</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MapLibre GL JS</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BSD-3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carte vectorielle 2D sans clé — déjà notre choix pour la bascule</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dessin</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maplibre-gl-draw</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dessin et édition de formes sur terrain 3D, 200 000 entités éditables</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches data</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deck.gl</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D F</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rendu GPU de millions de points, heatmaps, arcs</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kepler.gl</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Application</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idées d'interface pour l'analyse spatiale</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S'INSPIRER</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TerriaJS</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Framework</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apache-2.0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalogue de dizaines de milliers de couches, Cesium + Leaflet</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S'INSPIRER</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe léger</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">globe.gl / three-globe</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minicarte en globe très léger, sans charger Cesium deux fois</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe minimal</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cobe</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe WebGL de 5 ko — candidat idéal pour la minicarte</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iTowns (IGN)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Framework</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT/CeCILL-B</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Framework 3D de l'IGN, pensé pour les données françaises</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuiles</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMTiles</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Format</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BSD</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un seul fichier de tuiles servi en statique — clé du mode hors ligne</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOT-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moteurs 3D et carto</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuiles</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protomaps</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de tuiles</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ODbL</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extrait OSM de l'Hérault embarquable, zéro appel réseau</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-01</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Base</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenStreetMap / Overpass</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ODbL</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E F</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Entités du terrain</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-02</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IGN Géoplateforme</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cadastre, orthophotos, altimétrie</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-03</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relief</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IGN RGE ALTI</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relief fin de Thau en local</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-04</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bathymétrie</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMODnet Bathymetry</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fond de la lagune et du golfe du Lion</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-05</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Littoral</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHOM data.shom.fr</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mixte</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit partiel</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte pour certains</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marées, courants, trait de côte</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-06</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Satellite</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copernicus Data Space</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence Copernicus</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sentinel-2 sur Thau, suivi des malaïgues</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-07</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isochrones</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valhalla / OpenRouteService</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT / clé</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORS: clé gratuite</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aller</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temps de trajet réels autour de l'étang</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-08</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Occupation du sol</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corine Land Cover</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usage des sols, embarquable</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-09</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bâti</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BD TOPO IGN</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1 E</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bâtiments avec hauteur — nourrit le traitement MATRIX</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEO-10</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données géo</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adresses</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAN</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aller</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géocodage</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-01</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vol</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenSky Network</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non commercial</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte conseillé</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avions</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-02</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mer</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AISStream</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clé gratuite</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navires — très pertinent pour Sète</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-03</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mer</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global Fishing Watch</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-BY</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effort de pêche en Méditerranée</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-04</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espace</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N2YO / Celestrak TLE</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N2YO: clé</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Satellites — Celestrak sans clé est préférable</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À MIGRER</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-05</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caméras</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalogue osiris (17 000 CCTV)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mosaïque multicam — filtrer sur la France</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-06</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caméras</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flux HLS publics DIR / Vinci</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flux</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caméras routières autour de Sète</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faible</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-07</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sanctions</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenSanctions</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-BY-NC partiel</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit en téléchargement</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Export statique embarqué, pas l'API</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-08</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actualité</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GDELT 2.0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F G</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niveau mondial d'INTEL</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-09</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actualité</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GDELT GEO 2.0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actualité géolocalisée en GeoJSON — directement posable sur le globe</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-10</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Énergie</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WRI Global Power Plant DB</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-BY</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 000 centrales — couche infrastructure</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-11</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réseau</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submarine Cable Map</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Câbles sous-marins</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-12</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réseau</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PeeringDB</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-BY</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte pour certains champs</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Points d'échange et data centers</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-13</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Menaces</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abuse.ch (URLhaus, Feodo)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC0</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clé gratuite depuis 2025</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infrastructure malveillante géolocalisée</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-14</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spatial</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NASA FIRMS</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domaine public</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAP_KEY</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feux actifs</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-15</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radio</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">radio-browser.info</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radios du monde</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-16</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radio</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radio Garden</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propriétaire</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON (CORS)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ouverture en fenêtre, pas d'encapsulation</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMITÉ</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-17</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vidéo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YouTube IFrame Player API</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propriétaire</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C D</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lecteur officiel embarqué — seule voie licite</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-18</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vidéo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twitch Embed</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propriétaire</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte dev pour l'API</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C D</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lecteur embarqué</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-19</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vidéo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hls.js</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apache-2.0</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lecture HLS dans la mosaïque multicam</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-20</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annuaire</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cipher387/osintmap (614 services)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registres et cadastres par pays — extraire la France</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-21</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT sources</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annuaire</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT-BIBLE 2026 (450+ outils)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentation</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sans objet</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veille</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Référence à jour, 35 sections</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEILLE</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-22</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requêtes</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ni5arga/sightline</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E F</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabarits de requêtes Overpass pour infrastructures</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-23</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rejeu</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AndrewCTF/velocity</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partiel</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Couches</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Historique de positions rejouable — même moteur Cesium</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-24</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tableau de bord</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">koala73/worldmonitor</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partiel</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taxonomie des couches et agrégation de presse</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-25</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kevtoe/worldview</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A F</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CesiumJS + vols, satellites, séismes, trafic, CCTV</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Globe</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VrushankPatel/godseye</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front-only comme nous, HUD tactique</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-27</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bureau</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0xhav0c/ARGUS</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON (Electron)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electron + Cesium : la piste de l'app installable</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-28</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gaopengbin/cesium-mcp</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dépôt</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piloter notre globe Cesium en langage naturel via MCP</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-29</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpiderFoot / theHarvester / Amass</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outils</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT / Apache</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON — serveur</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incompatible navigateur</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÉCARTÉ</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-30</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personnes</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sherlock / Maigret / WhatsMyName</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outils</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON — serveur</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enquête sur des personnes — hors éthique du projet</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÉCARTÉ</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSI-31</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSINT outils</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payant</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shodan / Censys / Maltego</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propriétaire</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAYANT</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oui</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maltego 3 000 à 7 500 EUR/an, Shodan 49 USD puis abonnement</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÉCARTÉ</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-01</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Splatting</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SuperSplat (PlayCanvas)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éditeur web</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nettoyer et publier un scan 3D dans le navigateur</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-02</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Splatting</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spark (World Labs)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open source</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rendu de splats sur Three.js, le plus actif en 2026</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-03</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Splatting</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">antimatter15/splat</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visionneuse WebGL minimale, peu de dépendances</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-04</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reconstruction</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenSplat / COLMAP / gsplat</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outils</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGPL / BSD</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON — hors ligne</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabriquer un splat d'un quartier de Sète, puis l'embarquer</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-05</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Format</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3D Tiles</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard OGC</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ouvert</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bâti de Thau en 3D servi en statique</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-06</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ville</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CityJSON / CityGML</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ouvert</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maquette urbaine normalisée</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-07</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Photo de rue</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panoramax (IGN)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vue de rue</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Photos de rue françaises, sans clé</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-08</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provenance</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C2PA / Content Credentials</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ouvert</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vérifier l'authenticité d'une image — anti-deepfake</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-09</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Archivage</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SingleFile</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extension</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGPL</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sans objet</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Figer une page web comme preuve datée</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEILLE</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMG-10</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imagerie et 3D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métadonnées</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExifTool</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outil</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perl Artistic</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse de photo — hors navigateur</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÉCARTÉ</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-01</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokens</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design tokens maison</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Méthode</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prolonger calques.js par des jetons de couleur et d'espacement</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À FAIRE</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-02</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animation</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSAP</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence standard gratuite</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animation du tracé cadastral</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-03</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animation</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motion One / Web Animations API</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT / natif</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alternative sans dépendance à GSAP</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-04</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Graphiques</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uPlot</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Courbes très légères pour les cadrans communaux</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-05</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Graphiques</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observable Plot / D3</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISC / BSD</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visualisations statistiques INSEE</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-06</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Graphe</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cytoscape.js / Sigma.js</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Graphe d'entités du territoire</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-07</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mosaïque</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Golden Layout / Dockview</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fenêtrage façon Bloomberg pour la multicam</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-08</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUD</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nexora (template HUD tactique)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Template</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">à vérifier</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Références visuelles : séquence de démarrage, texte brouillé</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S'INSPIRER</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faible</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-09</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Icônes</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lucide / Tabler Icons</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu d'icônes</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remplacer les emojis par un jeu cohérent</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-10</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Typo</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inter / JetBrains Mono</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Police</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OFL</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisibilité des chiffres — exigence récurrente</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UIX-11</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Design et interface</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accessibilité</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contraste WCAG</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Méthode</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les cases translucides doivent rester lisibles</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À FAIRE</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-01</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Résolveur</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unpaywall</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Courriel en paramètre</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dit si une version libre existe</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-02</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catalogue</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAlex</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC0</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Courriel conseillé</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250 M de travaux</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-03</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Europe</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open Research Europe</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-BY</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indirect</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Édition ouverte UE — lue via OpenAIRE et DOI</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À RELIER</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-04</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Europe</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Europe PMC</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUCUNE CLÉ</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40 M de notices, 10 req/s</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-05</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Europe</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORDIS</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs F</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Projets financés par l'UE et leurs budgets</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-06</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Europe</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data.europa.eu</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données publiques des 27</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-07</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métadonnées</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crossref</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC0</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOI vers référence citable</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-08</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAL</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ifremer et universités de Montpellier sur Thau</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-09</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theses.fr</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docs</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thèses françaises</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-10</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrimoine</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gallica (BnF)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API SRU</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Histoire locale</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartes et presse anciennes de Sète</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCI-11</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science et documents</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payant</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scopus / Web of Science</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Base</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propriétaire</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAYANT</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence établissement</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors budget et inutile ici</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÉCARTÉ</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-01</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presse</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flux RSS locaux</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flux</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI (via proxy)</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Midi Libre, Occitanie Tribune — attention au CORS</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-02</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Encyclopédie</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wikidata SPARQL</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC0</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Graphe d'entités du territoire</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-03</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistiques</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INSEE melodi</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compte</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Séries statistiques communales</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-04</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistiques</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eurostat</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niveau régional et national comparé</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-05</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistiques</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banque mondiale</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC-BY</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niveau mondial d'INTEL</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-06</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Droit</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Légifrance via PISTE</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMPTE PISTE</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Le site public suffit sans compte</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-07</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Délibérations des conseils municipaux</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vie locale — à verser dans la base Thau</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À FAIRE</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-08</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Annuaire des associations (RNA)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeu de données</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consigne explicite : associations, clubs, vie locale</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INF-09</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agendas culturels OpenAgenda</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence ouverte</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clé gratuite</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Événements autour de l'étang</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉVALUER</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-01</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service Worker + Cache API</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natif</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rendre l'app utilisable sans réseau</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-02</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IndexedDB</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natif</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stocker les données du territoire côté navigateur</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À PRENDRE</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-03</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SQLite WASM</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliothèque</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domaine public</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hors ligne</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Base interrogeable embarquée</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-04</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bureau</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tauri</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Framework</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App installable légère — décision D1 de la feuille de route</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À ÉTUDIER</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moyenne</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-05</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bureau</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electron</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Framework</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plus lourd que Tauri, mais ARGUS prouve que ça marche avec Cesium</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basse</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-06</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soleil</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcul solaire local</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module maison</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIT</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SunCalc</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hauteur, azimut, ombres, lune — 100% local</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-07</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contournement</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proxy CORS</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Service</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit ou payant</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variable</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NON</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C G</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casserait le modèle sans serveur — à éviter</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RISQUE</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEC-08</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technique</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualité</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tests Node natifs</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outil</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natif</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gratuit</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUI</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualité</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3480 tests en place</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN PLACE</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haute</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N103"/>
+</worksheet>
 </file>